--- a/docs/piloto/plantilla-analisis.xlsx
+++ b/docs/piloto/plantilla-analisis.xlsx
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B34" s="9">
-        <f>IF(OR(B8="",B28="",B30="",B32=""),"Faltan datos",IF(AND(B8="Cumple",B28="Cumple",B30="Cumple",B32="Cumple"),"Evaluar Demo 5","Iterar con lo que mostró el piloto"))</f>
+        <f>IF(OR(B8="",B28="",B30="",B32=""),"Faltan datos",IF(AND(B8="Cumple",B28="Cumple",B30="Cumple",B32="Cumple"),"Evaluar Demo 6","Iterar con lo que mostró el piloto"))</f>
         <v/>
       </c>
     </row>
